--- a/data/device_properties/ibm/ibm_torino_sampled_10q/ibm_torino_sampled_10q_2025-11-09.xlsx
+++ b/data/device_properties/ibm/ibm_torino_sampled_10q/ibm_torino_sampled_10q_2025-11-09.xlsx
@@ -2547,7 +2547,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cz0_1</t>
+          <t>cz1_0</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2625,7 +2625,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>cz0_3</t>
+          <t>cz3_0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2703,7 +2703,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>cz8_9</t>
+          <t>cz9_8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>9,8</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cz5_6</t>
+          <t>cz6_5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2859,7 +2859,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cz4_7</t>
+          <t>cz7_4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>7,4</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cz3_6</t>
+          <t>cz6_3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>6,3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3015,7 +3015,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cz7_9</t>
+          <t>cz9_7</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>9,7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cz4_5</t>
+          <t>cz5_4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>5,4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3171,7 +3171,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cz1_2</t>
+          <t>cz2_1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3249,7 +3249,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rzz0_1</t>
+          <t>rzz1_0</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3327,7 +3327,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rzz0_3</t>
+          <t>rzz3_0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>rzz8_9</t>
+          <t>rzz9_8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>9,8</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3483,7 +3483,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>rzz5_6</t>
+          <t>rzz6_5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3561,7 +3561,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>rzz4_7</t>
+          <t>rzz7_4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>7,4</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3639,7 +3639,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>rzz3_6</t>
+          <t>rzz6_3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>6,3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3717,7 +3717,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>rzz7_9</t>
+          <t>rzz9_7</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>9,7</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3795,7 +3795,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>rzz4_5</t>
+          <t>rzz5_4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>5,4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>rzz1_2</t>
+          <t>rzz2_1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">

--- a/data/device_properties/ibm/ibm_torino_sampled_10q/ibm_torino_sampled_10q_2025-11-09.xlsx
+++ b/data/device_properties/ibm/ibm_torino_sampled_10q/ibm_torino_sampled_10q_2025-11-09.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'name': 'lf_10', 'qubits': [0, 1, 2, 3, 4, 5, 6, 7, 8, 9]}]</t>
+          <t>[{"name": "lf_10", "qubits": [0, 1, 2, 3, 4, 5, 6, 7, 8, 9]}]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[2]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[2]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[2]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[2]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[2]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>[0, 1]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>[1, 0]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>[0, 3]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>[3, 0]</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>[8, 9]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>[9, 8]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>[5, 6]</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>[6, 5]</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>[4, 7]</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>7,4</t>
+          <t>[7, 4]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>[3, 6]</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>6,3</t>
+          <t>[6, 3]</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>[7, 9]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9,7</t>
+          <t>[9, 7]</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>[4, 5]</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>[5, 4]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>[1, 2]</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>[2, 1]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>[0, 1]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>[1, 0]</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>[0, 3]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>[3, 0]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>[8, 9]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>[9, 8]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>[5, 6]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>[6, 5]</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>[4, 7]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>7,4</t>
+          <t>[7, 4]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>[3, 6]</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6,3</t>
+          <t>[6, 3]</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>[7, 9]</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9,7</t>
+          <t>[9, 7]</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>[4, 5]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>[5, 4]</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>[1, 2]</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>[2, 1]</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[2]</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[2]</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>[4]</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>[8]</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
